--- a/VerveStacks_MEX_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MEX_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF242A20-CB69-4F5B-8DB5-5FDDB4EF0D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9403849B-C0D5-4943-84C5-C010CDE3CB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5126,7 +5126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{857AA3C0-C99E-416E-AEF0-3965BDD449D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D01382E-419F-4EFA-B75B-4E5152003175}">
   <dimension ref="B2:AF791"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23483,7 +23483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218D0F68-E239-4BF7-AAA6-A27BD943C826}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8E4356-ADDF-4EAD-B15A-5C415396CC5B}">
   <dimension ref="B9:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_MEX_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_MEX_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_MEX_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9403849B-C0D5-4943-84C5-C010CDE3CB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EEB8685-8144-470A-8705-4CEE1BABF418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5126,7 +5126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D01382E-419F-4EFA-B75B-4E5152003175}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A8794A8-8D6B-4D06-8911-0D89DC0F4331}">
   <dimension ref="B2:AF791"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23483,7 +23483,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8E4356-ADDF-4EAD-B15A-5C415396CC5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB57826-1271-476D-80EC-AC9132575DE1}">
   <dimension ref="B9:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
